--- a/257/food/tm2026-sm.xlsx
+++ b/257/food/tm2026-sm.xlsx
@@ -1133,7 +1133,7 @@
       </c>
       <c r="H2" s="59" t="inlineStr">
         <is>
-          <t>Контаев Руслан-Бек Вахидович</t>
+          <t xml:space="preserve">Контаев Руслан-Бек Вахидович </t>
         </is>
       </c>
       <c r="I2" s="60" t="n"/>
@@ -7114,9 +7114,9 @@
   <mergeCells count="14">
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>

--- a/257/food/tm2026-sm.xlsx
+++ b/257/food/tm2026-sm.xlsx
@@ -7115,8 +7115,8 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C62:D62"/>
     <mergeCell ref="C195:D195"/>
     <mergeCell ref="C157:D157"/>
     <mergeCell ref="C138:D138"/>
